--- a/data/belgrad/Veriler.xlsx
+++ b/data/belgrad/Veriler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\belgrad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2541FF59-46A0-4433-AD50-8AFFE15E4E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186DB1E5-615C-4317-9BF4-AE0E5BBEC9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2784" yWindow="3456" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -2399,6 +2399,7 @@
     <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">

--- a/data/belgrad/Veriler.xlsx
+++ b/data/belgrad/Veriler.xlsx
@@ -5,35 +5,554 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\belgrad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Downloads\bozankaya_ssh_takip (1)\bozankaya_ssh_takip\data\belgrad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25608644-09EE-4A52-87C0-583CF5FB569A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BAA79B-C0CA-4500-901D-9D2371C8C714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sayfa2" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="199">
+  <si>
+    <t>Traction_Converter</t>
+  </si>
+  <si>
+    <t>Auxiliary_Power_Unit</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>ESS_Battery_Box</t>
+  </si>
+  <si>
+    <t>Pantograf</t>
+  </si>
+  <si>
+    <t>HSCB</t>
+  </si>
+  <si>
+    <t>TCMS</t>
+  </si>
+  <si>
+    <t>Master_Controler</t>
+  </si>
+  <si>
+    <t>HMI</t>
+  </si>
+  <si>
+    <t>Bogie</t>
+  </si>
+  <si>
+    <t>Gearbox</t>
+  </si>
+  <si>
+    <t>Wheel</t>
+  </si>
+  <si>
+    <t>Brake_System</t>
+  </si>
+  <si>
+    <t>Lubrication_System</t>
+  </si>
+  <si>
+    <t>Sanding_System</t>
+  </si>
+  <si>
+    <t>Hydraulic_Piping</t>
+  </si>
+  <si>
+    <t>Passenger_HVAC_System</t>
+  </si>
+  <si>
+    <t>Driver_HVAC_System</t>
+  </si>
+  <si>
+    <t>E_Kabinet</t>
+  </si>
+  <si>
+    <t>Cab_Desk</t>
+  </si>
+  <si>
+    <t>Cable_Duct</t>
+  </si>
+  <si>
+    <t>CCTV</t>
+  </si>
+  <si>
+    <t>Passenger_Information</t>
+  </si>
+  <si>
+    <t>Internal_Light</t>
+  </si>
+  <si>
+    <t>External_Light</t>
+  </si>
+  <si>
+    <t>Gangway_Articulation</t>
+  </si>
+  <si>
+    <t>Couplers</t>
+  </si>
+  <si>
+    <t>Suspantion_Damper</t>
+  </si>
+  <si>
+    <t>Door_System</t>
+  </si>
+  <si>
+    <t>Light_Barrier</t>
+  </si>
+  <si>
+    <t>Horn_Bell</t>
+  </si>
+  <si>
+    <t>Wiper_System</t>
+  </si>
+  <si>
+    <t>Fire_System</t>
+  </si>
+  <si>
+    <t>Signalization</t>
+  </si>
+  <si>
+    <t>Radio</t>
+  </si>
+  <si>
+    <t>Event_Recorder</t>
+  </si>
+  <si>
+    <t>Internal_Trim</t>
+  </si>
+  <si>
+    <t>External_Trim</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>Driver_Seat</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Medcom</t>
+  </si>
+  <si>
+    <t>HBL</t>
+  </si>
+  <si>
+    <t>Bozankaya</t>
+  </si>
+  <si>
+    <t>MİNEL</t>
+  </si>
+  <si>
+    <t>Secheron</t>
+  </si>
+  <si>
+    <t>ALFA UNİON</t>
+  </si>
+  <si>
+    <t>Wicov</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Hanning&amp;Kall</t>
+  </si>
+  <si>
+    <t>SKF</t>
+  </si>
+  <si>
+    <t>HISPACOLD</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>BOZANKAYA</t>
+  </si>
+  <si>
+    <t>NOVATRONİK</t>
+  </si>
+  <si>
+    <t>ERA</t>
+  </si>
+  <si>
+    <t>HÜBNER GmbH</t>
+  </si>
+  <si>
+    <t>IFE</t>
+  </si>
+  <si>
+    <t>Alfa UNION</t>
+  </si>
+  <si>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>Hanning&amp;Kahl</t>
+  </si>
+  <si>
+    <t>MEDCOM</t>
+  </si>
+  <si>
+    <t>Sazcılar</t>
+  </si>
+  <si>
+    <t>DORAGLASS</t>
+  </si>
+  <si>
+    <t>Bozankya</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis. Aux ekipmanı</t>
+  </si>
+  <si>
+    <t>DBS Şalteri</t>
+  </si>
+  <si>
+    <t>Batarya Hücreleri</t>
+  </si>
+  <si>
+    <t>ESS Batarya Hücreleri</t>
+  </si>
+  <si>
+    <t>Pantograf Mekanızması</t>
+  </si>
+  <si>
+    <t>TCMS CAN/Ethernet geçiş modülü</t>
+  </si>
+  <si>
+    <t>İvme Kolu Encoder</t>
+  </si>
+  <si>
+    <t>Dişli Kutusu</t>
+  </si>
+  <si>
+    <t>Fren Disk</t>
+  </si>
+  <si>
+    <t>Yağlama Nozulu</t>
+  </si>
+  <si>
+    <t>Kumlama Nozulu</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Evaporatör  Fan</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Evaporatör  Fan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP Kamera </t>
+  </si>
+  <si>
+    <t>YBS Amfi</t>
+  </si>
+  <si>
+    <t>Sürücü Aydınlatma</t>
+  </si>
+  <si>
+    <t>Ön/arka sinyal lambası</t>
+  </si>
+  <si>
+    <t>Kuplor Asansörü Switch</t>
+  </si>
+  <si>
+    <t>Kapı Kontrol Ünitesi</t>
+  </si>
+  <si>
+    <t>Işık Bariyeri Sensörü</t>
+  </si>
+  <si>
+    <t>Silecek Mekanızması</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Konverter</t>
+  </si>
+  <si>
+    <t>ESS Batarya Kontrol Kartı (SCL)</t>
+  </si>
+  <si>
+    <t>Pantograf Manuel kaldırma kolu</t>
+  </si>
+  <si>
+    <t>TCMS I/O haberleşme interface</t>
+  </si>
+  <si>
+    <t>İvme Kolu Kablolama</t>
+  </si>
+  <si>
+    <t>Yatay/dikey damper</t>
+  </si>
+  <si>
+    <t>Fren Kaliper</t>
+  </si>
+  <si>
+    <t>Yağlama Tankı</t>
+  </si>
+  <si>
+    <t>Kumlama Tankı</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Kablolama</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Kablolama</t>
+  </si>
+  <si>
+    <t>Analog Ayna Kamera</t>
+  </si>
+  <si>
+    <t>Yolcu Aydınlatma</t>
+  </si>
+  <si>
+    <t>Yan sinyal lambası</t>
+  </si>
+  <si>
+    <t>Kuplör Asansör Motoru</t>
+  </si>
+  <si>
+    <t>Kapı Switchler</t>
+  </si>
+  <si>
+    <t>Işık Bariyeri Reflektör</t>
+  </si>
+  <si>
+    <t>Silecek Kontrol kartı</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Kontrol Kartı</t>
+  </si>
+  <si>
+    <t>ESS Batarya Konnektörler</t>
+  </si>
+  <si>
+    <t>Pantograf Esnek Halat</t>
+  </si>
+  <si>
+    <t>İvme Kolu Soket</t>
+  </si>
+  <si>
+    <t>Primer Süspansiyon</t>
+  </si>
+  <si>
+    <t>Fren Sensörler</t>
+  </si>
+  <si>
+    <t>Yağlama Kontrol ünitesi</t>
+  </si>
+  <si>
+    <t>Kumlama Kontrol ünitesi</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Koltuk altı ısıtıcı</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Kompresör</t>
+  </si>
+  <si>
+    <t>Ayna Kamera Ekranı</t>
+  </si>
+  <si>
+    <t>Tepe Lambası</t>
+  </si>
+  <si>
+    <t>Kuplor Kontrol sinyal kabloları</t>
+  </si>
+  <si>
+    <t>Kapı Hassas Kenar kablolaması</t>
+  </si>
+  <si>
+    <t>Silecek Kolları ve Bıçakları</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Röle</t>
+  </si>
+  <si>
+    <t>ESS Batarya Fuse Kitleri</t>
+  </si>
+  <si>
+    <t>Pantograf Limit Switch</t>
+  </si>
+  <si>
+    <t>İvme Kolu Mekanızma</t>
+  </si>
+  <si>
+    <t>Sekonder Süspansiyon</t>
+  </si>
+  <si>
+    <t>Fren Hidrolik/pnömatik borulama</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Kompresör</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Kondenser Fan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamera </t>
+  </si>
+  <si>
+    <t>CCTV/YBS Bilgisayar</t>
+  </si>
+  <si>
+    <t>Far</t>
+  </si>
+  <si>
+    <t>Kuplor Soket bağlantıları</t>
+  </si>
+  <si>
+    <t>Kapı Kanatları</t>
+  </si>
+  <si>
+    <t>Silecek Hortumu</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Sigorta</t>
+  </si>
+  <si>
+    <t>ESS Batarya BMS Kartı</t>
+  </si>
+  <si>
+    <t>Pantograf Kollektör Kafası</t>
+  </si>
+  <si>
+    <t>İvme Kolu Switch</t>
+  </si>
+  <si>
+    <t>Seviye Sensörü</t>
+  </si>
+  <si>
+    <t>Fren Ray Freni</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Kondenser Fan</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Kontrol ünitesi</t>
+  </si>
+  <si>
+    <t>Kayıt Cihazı (NVR)</t>
+  </si>
+  <si>
+    <t>Kuplor Elektrik Kafa Motoru</t>
+  </si>
+  <si>
+    <t>Kapı Üstü Buton</t>
+  </si>
+  <si>
+    <t>Silecek Mil Bağlantısı</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Batary charger</t>
+  </si>
+  <si>
+    <t>Pantograf Motoru</t>
+  </si>
+  <si>
+    <t>Fren Akümülatör</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Kontrol ünitesi</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Rezistans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCTV Kablolaması </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCTV/YBS Display Arka Dış </t>
+  </si>
+  <si>
+    <t>Kuplor Kafa Switch</t>
+  </si>
+  <si>
+    <t>Kapı Kablolama</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Kontaktör</t>
+  </si>
+  <si>
+    <t>Pantograf Soket</t>
+  </si>
+  <si>
+    <t>Fren Hidrolik pompa Ünitesi</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Rezistans</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Sıcaklık sensörleri</t>
+  </si>
+  <si>
+    <t>CCTV Ekran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCTV/YBS Display Ön Dış </t>
+  </si>
+  <si>
+    <t>Kapı Konnektör</t>
+  </si>
+  <si>
+    <t>Tahrik Konvertörü Sis.  Fan Sistemi</t>
+  </si>
+  <si>
+    <t>Pantograf YG Kablolama</t>
+  </si>
+  <si>
+    <t>Fren HPU kontrol ünitesi</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Sıcaklık sensörleri</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü Termik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCTV/YBS Display Yan Dış </t>
+  </si>
+  <si>
+    <t>Fren Rezistörü</t>
+  </si>
+  <si>
+    <t>Pantograf Lineer aktuator</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Sigorta</t>
+  </si>
+  <si>
+    <t>HVAC Sürücü  Sigorta</t>
+  </si>
+  <si>
+    <t>CCTV/YBS Kabin mikrofonu</t>
+  </si>
+  <si>
+    <t>HVAC Yolcu Termik</t>
+  </si>
+  <si>
+    <t>CCTV/YBS Kablolama</t>
+  </si>
+  <si>
+    <t>CCTV/YBS Sürücü Ekranı</t>
+  </si>
+  <si>
+    <t>CCTV/YBS Yolcu Alanı Orta Ekran</t>
+  </si>
   <si>
     <t>tram_id</t>
   </si>
@@ -62,70 +581,138 @@
     <t>A-Kritik/Emniyet Riski</t>
   </si>
   <si>
-    <t>Bozankaya</t>
-  </si>
-  <si>
     <t>(I) İlk Defa Karşılaşılan Arıza</t>
   </si>
   <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>B-Yüksek/Operasyon Engeller</t>
+  </si>
+  <si>
+    <t>Müşteri</t>
+  </si>
+  <si>
+    <t>(II) Aynı Araçta Tekrarlayan Arıza</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>C-Hafif/Kısıtlı Operasyon</t>
+  </si>
+  <si>
+    <t>Tedarikçi</t>
+  </si>
+  <si>
+    <t>(III) Farklı Araçlarda Tekrarlayan Arıza</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>D-Arıza Değildir</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>BELGRAD</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>B-Yüksek/Operasyon Engeller</t>
-  </si>
-  <si>
-    <t>Müşteri</t>
-  </si>
-  <si>
-    <t>(II) Aynı Araçta Tekrarlayan Arıza</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>C-Hafif/Kısıtlı Operasyon</t>
-  </si>
-  <si>
-    <t>Tedarikçi</t>
-  </si>
-  <si>
-    <t>(III) Farklı Araçlarda Tekrarlayan Arıza</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t>D-Arıza Değildir</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-41F]d\ mmmm\ yy;@"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -133,18 +720,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -157,7 +851,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -167,44 +861,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -231,14 +925,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -265,6 +977,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -276,371 +1006,1527 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AO18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="W3" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="X3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y3" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="10"/>
+      <c r="AN3" s="10"/>
+    </row>
+    <row r="4" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="W4" s="13"/>
+      <c r="X4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="10"/>
+    </row>
+    <row r="5" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="10"/>
+      <c r="AN5" s="10"/>
+    </row>
+    <row r="6" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="W6" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="10"/>
+      <c r="AN6" s="10"/>
+    </row>
+    <row r="7" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="11"/>
+      <c r="AK7" s="11"/>
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="10"/>
+    </row>
+    <row r="8" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="11"/>
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="10"/>
+      <c r="AN8" s="10"/>
+    </row>
+    <row r="9" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="12"/>
+      <c r="AC9" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="10"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="11"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="10"/>
+    </row>
+    <row r="10" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="11"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="11"/>
+      <c r="AK10" s="11"/>
+      <c r="AL10" s="11"/>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="10"/>
+    </row>
+    <row r="11" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="12"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
+      <c r="AJ11" s="11"/>
+      <c r="AK11" s="11"/>
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="10"/>
+      <c r="AN11" s="10"/>
+    </row>
+    <row r="12" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="10"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+      <c r="AN13" s="10"/>
+    </row>
+    <row r="14" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="10"/>
+      <c r="AN14" s="10"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
+      <c r="AL15" s="10"/>
+      <c r="AM15" s="10"/>
+      <c r="AN15" s="10"/>
+    </row>
+    <row r="16" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13"/>
+      <c r="AF16" s="13"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="10"/>
+      <c r="AN16" s="10"/>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="10"/>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+      <c r="AN17" s="10"/>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="35.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>181</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>1531</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+        <v>43</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>1532</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
+        <v>189</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>1533</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
+        <v>193</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1534</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>1535</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>1536</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>1537</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>1538</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>1539</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>1540</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>1541</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>1542</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>1543</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>1544</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>1545</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>1546</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>1547</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>1548</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>1549</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>1550</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>1551</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>1552</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>1553</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>1554</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>1555</v>
       </c>
     </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/data/belgrad/Veriler.xlsx
+++ b/data/belgrad/Veriler.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Downloads\bozankaya_ssh_takip (1)\bozankaya_ssh_takip\data\belgrad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\belgrad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BAA79B-C0CA-4500-901D-9D2371C8C714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61F2F6D-DB29-42AF-A000-DDEE0BD6DA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="200">
   <si>
     <t>Traction_Converter</t>
   </si>
@@ -584,6 +597,9 @@
     <t>(I) İlk Defa Karşılaşılan Arıza</t>
   </si>
   <si>
+    <t>BELGRAD</t>
+  </si>
+  <si>
     <t>SA</t>
   </si>
   <si>
@@ -617,15 +633,16 @@
     <t>M</t>
   </si>
   <si>
-    <t>BELGRAD</t>
+    <t>İşçilik</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-41F]d\ mmmm\ yy;@"/>
+    <numFmt numFmtId="165" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -784,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -833,6 +850,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2315,15 +2333,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="5" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>177</v>
       </c>
@@ -2342,8 +2361,11 @@
       <c r="F1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1531</v>
       </c>
@@ -2362,109 +2384,112 @@
       <c r="F2" s="17" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1532</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1533</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1534</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1535</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1536</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1537</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1538</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1539</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1540</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1541</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1542</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1543</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1544</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1545</v>
       </c>

--- a/data/belgrad/Veriler.xlsx
+++ b/data/belgrad/Veriler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\belgrad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61F2F6D-DB29-42AF-A000-DDEE0BD6DA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96940289-A0E0-4E0D-9A51-5541C628CA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="201">
   <si>
     <t>Traction_Converter</t>
   </si>
@@ -634,6 +634,9 @@
   </si>
   <si>
     <t>İşçilik</t>
+  </si>
+  <si>
+    <t>Buzzer</t>
   </si>
 </sst>
 </file>
@@ -1513,6 +1516,9 @@
       <c r="AL3" s="11"/>
       <c r="AM3" s="10"/>
       <c r="AN3" s="10"/>
+      <c r="AO3" s="10" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="4" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -1591,6 +1597,7 @@
       <c r="AL4" s="11"/>
       <c r="AM4" s="10"/>
       <c r="AN4" s="10"/>
+      <c r="AO4" s="10"/>
     </row>
     <row r="5" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
@@ -1663,6 +1670,7 @@
       <c r="AL5" s="11"/>
       <c r="AM5" s="10"/>
       <c r="AN5" s="10"/>
+      <c r="AO5" s="10"/>
     </row>
     <row r="6" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
@@ -1733,6 +1741,7 @@
       <c r="AL6" s="11"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="10"/>
+      <c r="AO6" s="10"/>
     </row>
     <row r="7" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
@@ -1799,6 +1808,7 @@
       <c r="AL7" s="11"/>
       <c r="AM7" s="10"/>
       <c r="AN7" s="10"/>
+      <c r="AO7" s="10"/>
     </row>
     <row r="8" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
@@ -1859,6 +1869,7 @@
       <c r="AL8" s="11"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="10"/>
+      <c r="AO8" s="10"/>
     </row>
     <row r="9" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
@@ -1917,6 +1928,7 @@
       <c r="AL9" s="11"/>
       <c r="AM9" s="10"/>
       <c r="AN9" s="10"/>
+      <c r="AO9" s="10"/>
     </row>
     <row r="10" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
@@ -1971,6 +1983,7 @@
       <c r="AL10" s="11"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="10"/>
+      <c r="AO10" s="10"/>
     </row>
     <row r="11" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
@@ -2023,6 +2036,7 @@
       <c r="AL11" s="11"/>
       <c r="AM11" s="10"/>
       <c r="AN11" s="10"/>
+      <c r="AO11" s="10"/>
     </row>
     <row r="12" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
@@ -2069,6 +2083,7 @@
       <c r="AL12" s="10"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="10"/>
+      <c r="AO12" s="10"/>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
@@ -2111,6 +2126,7 @@
       <c r="AL13" s="10"/>
       <c r="AM13" s="10"/>
       <c r="AN13" s="10"/>
+      <c r="AO13" s="10"/>
     </row>
     <row r="14" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
@@ -2155,6 +2171,7 @@
       <c r="AL14" s="10"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="10"/>
+      <c r="AO14" s="10"/>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
@@ -2197,6 +2214,7 @@
       <c r="AL15" s="10"/>
       <c r="AM15" s="10"/>
       <c r="AN15" s="10"/>
+      <c r="AO15" s="10"/>
     </row>
     <row r="16" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
@@ -2241,8 +2259,9 @@
       <c r="AL16" s="10"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="10"/>
-    </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="AO16" s="10"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2283,8 +2302,9 @@
       <c r="AL17" s="10"/>
       <c r="AM17" s="10"/>
       <c r="AN17" s="10"/>
-    </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="AO17" s="10"/>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2325,6 +2345,7 @@
       <c r="AL18" s="10"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
